--- a/docentes/Miguel Lopez Yadira - Estadisticos 20221.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20221.xlsx
@@ -682,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20221.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20221.xlsx
@@ -548,16 +548,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>36</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>92.31</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -622,7 +625,7 @@
         <v>92.31</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20221.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,24 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
   </si>
 </sst>
 </file>
@@ -483,10 +465,10 @@
         <v>39</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>3</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>36</v>
@@ -495,7 +477,7 @@
         <v>92.31</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -548,19 +530,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>92.31</v>
+        <v>97.44</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -613,19 +595,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>92.31</v>
+        <v>97.44</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -665,52 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920180</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920363</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Miguel Lopez Yadira - Estadisticos 20221.xlsx
+++ b/docentes/Miguel Lopez Yadira - Estadisticos 20221.xlsx
@@ -607,7 +607,7 @@
         <v>97.44</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
